--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
@@ -571,22 +571,25 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>77.78</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -940,22 +943,25 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>77.78</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="5" spans="1:11">

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
@@ -501,25 +501,25 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -536,25 +536,25 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -571,25 +571,25 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>22.22</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -693,22 +693,25 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>93.33</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>6.67</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -725,22 +728,25 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.6</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -757,22 +763,25 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -789,22 +798,25 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>6.67</v>
       </c>
     </row>
   </sheetData>
@@ -873,25 +885,25 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>80</v>
+        <v>93.33</v>
       </c>
       <c r="H2" s="1">
-        <v>20</v>
+        <v>6.67</v>
       </c>
       <c r="I2" s="2">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -908,25 +920,25 @@
         <v>18</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -943,25 +955,25 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>22.22</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>77.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -978,19 +990,19 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H5" s="1">
-        <v>26.67</v>
+        <v>33.33</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>1</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
@@ -618,13 +618,13 @@
         <v>26.67</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -798,25 +798,25 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H5" s="1">
-        <v>33.33</v>
+        <v>26.67</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -990,25 +990,25 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H5" s="1">
-        <v>33.33</v>
+        <v>26.67</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
@@ -990,19 +990,19 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>73.33</v>
+        <v>93.33</v>
       </c>
       <c r="H5" s="1">
-        <v>26.67</v>
+        <v>6.67</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
@@ -885,19 +885,19 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20221.xlsx
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
